--- a/docs/product/Timeline.xlsx
+++ b/docs/product/Timeline.xlsx
@@ -194,7 +194,7 @@
     <t>Tunable late-fee rate, grace period, rent-change notice window — Admin tunes from UI.</t>
   </si>
   <si>
-    <t>Organisation Management</t>
+    <t>Organization Management</t>
   </si>
   <si>
     <t>SAAS layer — public org sign-up + Super Admin approval; Subscription Plans (Basic/Standard/Premium) capping active users; org lifecycle.</t>
